--- a/Example/Invoice.xlsx
+++ b/Example/Invoice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\OysterReport\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22B20D8-A905-4BB9-9E55-1ADE82206607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F57DEA5-71B1-44F1-9C5A-D14D68CE1310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41700" yWindow="5970" windowWidth="22575" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23025" yWindow="2355" windowWidth="22575" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書" sheetId="1" r:id="rId1"/>
@@ -199,7 +199,47 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>発行日  {{IssueDate}}</t>
+    <t>{{DeliveryDate}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{TotalAmount}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{No}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{Item}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{Qty}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{Price}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{Amount}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{SubTotal}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{Tax}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{BillingTo}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>発行日  {{InvoiceDate}}</t>
     <rPh sb="0" eb="2">
       <t>ハッコウ</t>
     </rPh>
@@ -209,51 +249,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>No {{IssueNo}}</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>{{Title}}</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>{{DeliveryDate}}</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>{{TotalAmount}}</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>{{No}}</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>{{Item}}</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>{{Qty}}</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>{{Price}}</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>{{Amount}}</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>{{SubTotal}}</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>{{Tax}}</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>{{BillingTo}}</t>
+    <t>No        {{InvoiceNo}}</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>{{Subject}}</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -265,7 +265,7 @@
     <numFmt numFmtId="5" formatCode="&quot;¥&quot;#,##0;&quot;¥&quot;\-#,##0"/>
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -368,6 +368,13 @@
     <font>
       <i/>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
@@ -502,7 +509,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -596,6 +603,18 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -614,10 +633,10 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="5" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -634,12 +653,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1197,14 +1210,14 @@
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="26"/>
       <c r="E3" s="6" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
       <c r="E4" s="7" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
@@ -1213,10 +1226,10 @@
       <c r="C5" s="10"/>
     </row>
     <row r="6" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="38"/>
+      <c r="B6" s="42"/>
       <c r="C6" s="10"/>
       <c r="D6" s="9"/>
     </row>
@@ -1225,14 +1238,14 @@
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="39"/>
+      <c r="A8" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="43"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A9" s="40"/>
-      <c r="B9" s="40"/>
+      <c r="A9" s="44"/>
+      <c r="B9" s="44"/>
       <c r="C9" s="2" t="s">
         <v>0</v>
       </c>
@@ -1252,60 +1265,60 @@
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="40"/>
+      <c r="B12" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="34"/>
       <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="47"/>
+      <c r="B13" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="35"/>
       <c r="E13" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
       <c r="E14" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
       <c r="E15" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
     </row>
     <row r="18" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="A18" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="44" t="s">
+      <c r="B18" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="48" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="43"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="45"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="49"/>
     </row>
     <row r="20" spans="1:5" ht="13.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1327,19 +1340,19 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="E22" s="27" t="s">
         <v>26</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="E22" s="27" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1518,7 +1531,7 @@
         <v>8</v>
       </c>
       <c r="E47" s="30" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -1529,7 +1542,7 @@
         <v>6</v>
       </c>
       <c r="E48" s="29" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1540,73 +1553,73 @@
         <v>9</v>
       </c>
       <c r="E49" s="28" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="33" t="s">
+      <c r="A50" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B50" s="33"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="33"/>
+      <c r="B50" s="37"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="37"/>
     </row>
     <row r="51" spans="1:5" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="34"/>
-      <c r="B51" s="34"/>
-      <c r="C51" s="34"/>
-      <c r="D51" s="34"/>
-      <c r="E51" s="34"/>
+      <c r="A51" s="38"/>
+      <c r="B51" s="38"/>
+      <c r="C51" s="38"/>
+      <c r="D51" s="38"/>
+      <c r="E51" s="38"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="34"/>
-      <c r="B52" s="34"/>
-      <c r="C52" s="34"/>
-      <c r="D52" s="34"/>
-      <c r="E52" s="34"/>
+      <c r="A52" s="38"/>
+      <c r="B52" s="38"/>
+      <c r="C52" s="38"/>
+      <c r="D52" s="38"/>
+      <c r="E52" s="38"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="34"/>
-      <c r="B53" s="34"/>
-      <c r="C53" s="34"/>
-      <c r="D53" s="34"/>
-      <c r="E53" s="34"/>
+      <c r="A53" s="38"/>
+      <c r="B53" s="38"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="38"/>
+      <c r="E53" s="38"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="35"/>
-      <c r="B54" s="35"/>
-      <c r="C54" s="35"/>
-      <c r="D54" s="35"/>
-      <c r="E54" s="35"/>
+      <c r="A54" s="39"/>
+      <c r="B54" s="39"/>
+      <c r="C54" s="39"/>
+      <c r="D54" s="39"/>
+      <c r="E54" s="39"/>
     </row>
     <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="36"/>
-      <c r="B55" s="36"/>
-      <c r="C55" s="36"/>
-      <c r="D55" s="36"/>
-      <c r="E55" s="36"/>
+      <c r="A55" s="40"/>
+      <c r="B55" s="40"/>
+      <c r="C55" s="40"/>
+      <c r="D55" s="40"/>
+      <c r="E55" s="40"/>
     </row>
     <row r="56" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="36"/>
-      <c r="B56" s="36"/>
-      <c r="C56" s="36"/>
-      <c r="D56" s="36"/>
-      <c r="E56" s="36"/>
+      <c r="A56" s="40"/>
+      <c r="B56" s="40"/>
+      <c r="C56" s="40"/>
+      <c r="D56" s="40"/>
+      <c r="E56" s="40"/>
     </row>
     <row r="57" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="36"/>
-      <c r="B57" s="36"/>
-      <c r="C57" s="36"/>
-      <c r="D57" s="36"/>
-      <c r="E57" s="36"/>
+      <c r="A57" s="40"/>
+      <c r="B57" s="40"/>
+      <c r="C57" s="40"/>
+      <c r="D57" s="40"/>
+      <c r="E57" s="40"/>
     </row>
     <row r="58" spans="1:5" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="37"/>
-      <c r="B58" s="37"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
+      <c r="A58" s="41"/>
+      <c r="B58" s="41"/>
+      <c r="C58" s="41"/>
+      <c r="D58" s="41"/>
+      <c r="E58" s="41"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="17"/>
@@ -1624,11 +1637,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
     <mergeCell ref="A50:E50"/>
     <mergeCell ref="A51:E54"/>
     <mergeCell ref="A55:E58"/>
@@ -1638,6 +1646,11 @@
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="C18:C19"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/Example/Invoice.xlsx
+++ b/Example/Invoice.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\OysterReport\Example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\machi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F57DEA5-71B1-44F1-9C5A-D14D68CE1310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F161E055-C9AD-4E8F-870F-352392EE584E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23025" yWindow="2355" windowWidth="22575" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5310" yWindow="630" windowWidth="23265" windowHeight="19470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書" sheetId="1" r:id="rId1"/>
@@ -509,7 +509,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -594,27 +594,12 @@
     <xf numFmtId="176" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -645,6 +630,9 @@
     <xf numFmtId="5" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -653,6 +641,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1214,8 +1220,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A4" s="33"/>
-      <c r="B4" s="33"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
       <c r="E4" s="7" t="s">
         <v>31</v>
       </c>
@@ -1226,10 +1232,10 @@
       <c r="C5" s="10"/>
     </row>
     <row r="6" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="42"/>
+      <c r="B6" s="37"/>
       <c r="C6" s="10"/>
       <c r="D6" s="9"/>
     </row>
@@ -1238,14 +1244,14 @@
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="43"/>
+      <c r="B8" s="38"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A9" s="44"/>
-      <c r="B9" s="44"/>
+      <c r="A9" s="39"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="2" t="s">
         <v>0</v>
       </c>
@@ -1265,60 +1271,60 @@
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="34"/>
+      <c r="C12" s="47"/>
       <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="35"/>
+      <c r="C13" s="48"/>
       <c r="E13" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
       <c r="E14" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
       <c r="E15" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
     </row>
     <row r="18" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="36" t="s">
+      <c r="A18" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="48" t="s">
+      <c r="C18" s="44" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="49"/>
+      <c r="A19" s="43"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="45"/>
     </row>
     <row r="20" spans="1:5" ht="13.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1345,10 +1351,10 @@
       <c r="B22" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C22" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="31" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="27" t="s">
@@ -1524,13 +1530,13 @@
       <c r="E46" s="19"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="13" t="s">
+      <c r="A47" s="49"/>
+      <c r="B47" s="49"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="30" t="s">
+      <c r="E47" s="51" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1557,69 +1563,69 @@
       </c>
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="37" t="s">
+      <c r="A50" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B50" s="37"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37"/>
+      <c r="B50" s="32"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
     </row>
     <row r="51" spans="1:5" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="38"/>
-      <c r="B51" s="38"/>
-      <c r="C51" s="38"/>
-      <c r="D51" s="38"/>
-      <c r="E51" s="38"/>
+      <c r="A51" s="33"/>
+      <c r="B51" s="33"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="33"/>
+      <c r="E51" s="33"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="38"/>
-      <c r="B52" s="38"/>
-      <c r="C52" s="38"/>
-      <c r="D52" s="38"/>
-      <c r="E52" s="38"/>
+      <c r="A52" s="33"/>
+      <c r="B52" s="33"/>
+      <c r="C52" s="33"/>
+      <c r="D52" s="33"/>
+      <c r="E52" s="33"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="38"/>
-      <c r="B53" s="38"/>
-      <c r="C53" s="38"/>
-      <c r="D53" s="38"/>
-      <c r="E53" s="38"/>
+      <c r="A53" s="33"/>
+      <c r="B53" s="33"/>
+      <c r="C53" s="33"/>
+      <c r="D53" s="33"/>
+      <c r="E53" s="33"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="39"/>
-      <c r="B54" s="39"/>
-      <c r="C54" s="39"/>
-      <c r="D54" s="39"/>
-      <c r="E54" s="39"/>
+      <c r="A54" s="34"/>
+      <c r="B54" s="34"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="34"/>
     </row>
     <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="40"/>
-      <c r="B55" s="40"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="40"/>
-      <c r="E55" s="40"/>
+      <c r="A55" s="35"/>
+      <c r="B55" s="35"/>
+      <c r="C55" s="35"/>
+      <c r="D55" s="35"/>
+      <c r="E55" s="35"/>
     </row>
     <row r="56" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="40"/>
-      <c r="B56" s="40"/>
-      <c r="C56" s="40"/>
-      <c r="D56" s="40"/>
-      <c r="E56" s="40"/>
+      <c r="A56" s="35"/>
+      <c r="B56" s="35"/>
+      <c r="C56" s="35"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
     </row>
     <row r="57" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="40"/>
-      <c r="B57" s="40"/>
-      <c r="C57" s="40"/>
-      <c r="D57" s="40"/>
-      <c r="E57" s="40"/>
+      <c r="A57" s="35"/>
+      <c r="B57" s="35"/>
+      <c r="C57" s="35"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
     </row>
     <row r="58" spans="1:5" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="41"/>
-      <c r="B58" s="41"/>
-      <c r="C58" s="41"/>
-      <c r="D58" s="41"/>
-      <c r="E58" s="41"/>
+      <c r="A58" s="36"/>
+      <c r="B58" s="36"/>
+      <c r="C58" s="36"/>
+      <c r="D58" s="36"/>
+      <c r="E58" s="36"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="17"/>
@@ -1637,6 +1643,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
     <mergeCell ref="A50:E50"/>
     <mergeCell ref="A51:E54"/>
     <mergeCell ref="A55:E58"/>
@@ -1646,11 +1657,6 @@
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="C18:C19"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/Example/Invoice.xlsx
+++ b/Example/Invoice.xlsx
@@ -1364,163 +1364,163 @@
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
       <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="18"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="27"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="11"/>
       <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="18"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="27"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
       <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="18"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="27"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="18"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="27"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
       <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="18"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="27"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="11"/>
       <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="18"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="27"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="18"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="27"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="18"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="27"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="18"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="27"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="18"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="27"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="18"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="27"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
       <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="18"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="27"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
       <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="18"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="27"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
       <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="18"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="27"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="11"/>
       <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="18"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="27"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
       <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="18"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="27"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="11"/>
       <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="18"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="27"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="11"/>
       <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="18"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="27"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
       <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="18"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="27"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="11"/>
       <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="18"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="27"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="11"/>
       <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="18"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="27"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="11"/>
       <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="18"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="27"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="11"/>
       <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="18"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="27"/>
     </row>
     <row r="46" spans="1:5" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14"/>
